--- a/artfynd/A 37078-2026 artfynd.xlsx
+++ b/artfynd/A 37078-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931988</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136931989</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136931990</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136931992</v>
       </c>
       <c r="B5" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37078-2026 artfynd.xlsx
+++ b/artfynd/A 37078-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931988</v>
       </c>
       <c r="B2" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136931989</v>
       </c>
       <c r="B3" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136931990</v>
       </c>
       <c r="B4" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136931992</v>
       </c>
       <c r="B5" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37078-2026 artfynd.xlsx
+++ b/artfynd/A 37078-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931988</v>
       </c>
       <c r="B2" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136931989</v>
       </c>
       <c r="B3" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136931990</v>
       </c>
       <c r="B4" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136931992</v>
       </c>
       <c r="B5" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37078-2026 artfynd.xlsx
+++ b/artfynd/A 37078-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136931992</v>
       </c>
       <c r="B5" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37078-2026 artfynd.xlsx
+++ b/artfynd/A 37078-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931988</v>
       </c>
       <c r="B2" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136931989</v>
       </c>
       <c r="B3" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136931990</v>
       </c>
       <c r="B4" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136931992</v>
       </c>
       <c r="B5" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37078-2026 artfynd.xlsx
+++ b/artfynd/A 37078-2026 artfynd.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Pär Eriksson</t>
+          <t>Pär Eriksson, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -892,7 +892,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Pär Eriksson</t>
+          <t>Pär Eriksson, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Pär Eriksson</t>
+          <t>Pär Eriksson, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
         <v>136931992</v>
       </c>
       <c r="B5" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Pär Eriksson</t>
+          <t>Pär Eriksson, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 37078-2026 artfynd.xlsx
+++ b/artfynd/A 37078-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931988</v>
       </c>
       <c r="B2" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pär Eriksson, Gillis Aronsson</t>
+          <t>Gillis Aronsson, Pär Eriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,7 +795,7 @@
         <v>136931989</v>
       </c>
       <c r="B3" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pär Eriksson, Gillis Aronsson</t>
+          <t>Gillis Aronsson, Pär Eriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -907,7 +907,7 @@
         <v>136931990</v>
       </c>
       <c r="B4" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pär Eriksson, Gillis Aronsson</t>
+          <t>Gillis Aronsson, Pär Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
         <v>136931992</v>
       </c>
       <c r="B5" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Pär Eriksson, Gillis Aronsson</t>
+          <t>Gillis Aronsson, Pär Eriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 37078-2026 artfynd.xlsx
+++ b/artfynd/A 37078-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931988</v>
       </c>
       <c r="B2" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136931989</v>
       </c>
       <c r="B3" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136931990</v>
       </c>
       <c r="B4" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136931992</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37078-2026 artfynd.xlsx
+++ b/artfynd/A 37078-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931988</v>
       </c>
       <c r="B2" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136931989</v>
       </c>
       <c r="B3" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136931990</v>
       </c>
       <c r="B4" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136931992</v>
       </c>
       <c r="B5" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37078-2026 artfynd.xlsx
+++ b/artfynd/A 37078-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136931992</v>
       </c>
       <c r="B5" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37078-2026 artfynd.xlsx
+++ b/artfynd/A 37078-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931988</v>
       </c>
       <c r="B2" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136931989</v>
       </c>
       <c r="B3" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136931990</v>
       </c>
       <c r="B4" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136931992</v>
       </c>
       <c r="B5" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37078-2026 artfynd.xlsx
+++ b/artfynd/A 37078-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136931992</v>
       </c>
       <c r="B5" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37078-2026 artfynd.xlsx
+++ b/artfynd/A 37078-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931988</v>
       </c>
       <c r="B2" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136931989</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136931990</v>
       </c>
       <c r="B4" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136931992</v>
       </c>
       <c r="B5" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37078-2026 artfynd.xlsx
+++ b/artfynd/A 37078-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136931992</v>
       </c>
       <c r="B5" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37078-2026 artfynd.xlsx
+++ b/artfynd/A 37078-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931988</v>
       </c>
       <c r="B2" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136931989</v>
       </c>
       <c r="B3" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136931990</v>
       </c>
       <c r="B4" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136931992</v>
       </c>
       <c r="B5" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37078-2026 artfynd.xlsx
+++ b/artfynd/A 37078-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931988</v>
       </c>
       <c r="B2" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136931989</v>
       </c>
       <c r="B3" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136931990</v>
       </c>
       <c r="B4" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136931992</v>
       </c>
       <c r="B5" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37078-2026 artfynd.xlsx
+++ b/artfynd/A 37078-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931988</v>
       </c>
       <c r="B2" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136931989</v>
       </c>
       <c r="B3" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136931990</v>
       </c>
       <c r="B4" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136931992</v>
       </c>
       <c r="B5" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37078-2026 artfynd.xlsx
+++ b/artfynd/A 37078-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931988</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136931989</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136931990</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136931992</v>
       </c>
       <c r="B5" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37078-2026 artfynd.xlsx
+++ b/artfynd/A 37078-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931988</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136931989</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136931990</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136931992</v>
       </c>
       <c r="B5" t="n">
-        <v>98302</v>
+        <v>98303</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37078-2026 artfynd.xlsx
+++ b/artfynd/A 37078-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136931988</v>
       </c>
       <c r="B2" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136931989</v>
       </c>
       <c r="B3" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136931990</v>
       </c>
       <c r="B4" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136931992</v>
       </c>
       <c r="B5" t="n">
-        <v>98303</v>
+        <v>98306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
